--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -599,7 +599,7 @@
     <row r="2" ht="33.75" customFormat="1" customHeight="1" s="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>RV  FALLON OWNERS  ASOCIATION MAINTENANCE PAYMENT TRACKER – SEP 2026</t>
+          <t>KADAMBA LAKE VIEW APARTMENT — MAINTENANCE PAYMENT TRACKER – SEP 2026</t>
         </is>
       </c>
     </row>
